--- a/ansys/ress.xlsx
+++ b/ansys/ress.xlsx
@@ -8,24 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UniFlight\ansys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61304AB4-AC55-475D-B451-7DB16763BD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ACEA17-CCC1-40D0-9599-5CA5170F88C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>H</t>
   </si>
@@ -68,12 +78,36 @@
   <si>
     <t>неизв</t>
   </si>
+  <si>
+    <t xml:space="preserve"> CX</t>
+  </si>
+  <si>
+    <t>Расчет аэродинамики в ANSYS</t>
+  </si>
+  <si>
+    <t>CY</t>
+  </si>
+  <si>
+    <t>0.0176 ... 0.0233</t>
+  </si>
+  <si>
+    <t>cy1</t>
+  </si>
+  <si>
+    <t>cy2</t>
+  </si>
+  <si>
+    <t>cx1</t>
+  </si>
+  <si>
+    <t>cx2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,16 +115,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -98,12 +162,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -440,7 +524,985 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cx</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.34841</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.34206999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38430999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C77-4DAF-9C7C-FD600DADA3F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.34688999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4C77-4DAF-9C7C-FD600DADA3F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4C77-4DAF-9C7C-FD600DADA3F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963330752"/>
+        <c:axId val="1963332000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963330752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963332000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963332000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963330752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cy</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$15:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$16:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.8096000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.294E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.4621000000000002E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D8E-46AE-970B-65057E894363}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$15:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$17:$F$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.7794000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6D8E-46AE-970B-65057E894363}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист2!$C$15:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист2!$C$18:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6D8E-46AE-970B-65057E894363}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963330752"/>
+        <c:axId val="1963332000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963330752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963332000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963332000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963330752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -996,6 +2058,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1029,6 +3123,85 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1238ACED-40BC-4056-9758-6478EAA59052}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>138113</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5017ED92-48A6-43A7-B9CD-D11FD681C1BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1414,4 +3587,154 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A57C479-0864-4605-A9D5-2F74B6600C23}">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>0.3</v>
+      </c>
+      <c r="D4">
+        <v>0.7</v>
+      </c>
+      <c r="E4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.34841</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.34206999999999999</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.38430999999999998</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.34688999999999998</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>0.3</v>
+      </c>
+      <c r="D15">
+        <v>0.7</v>
+      </c>
+      <c r="E15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F15">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.8096000000000001E-2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1.294E-2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>8.4621000000000002E-3</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.7794000000000001E-2</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="I29">
+        <v>2.3300000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>